--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:30:34+00:00</t>
+    <t>2026-06-16T13:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:53:28+00:00</t>
+    <t>2026-06-16T14:51:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:51:07+00:00</t>
+    <t>2026-06-17T12:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:15:06+00:00</t>
+    <t>2026-06-17T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:49:22+00:00</t>
+    <t>2026-06-17T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:07:59+00:00</t>
+    <t>2026-06-17T15:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:48:42+00:00</t>
+    <t>2026-06-18T10:03:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:03:06+00:00</t>
+    <t>2026-06-18T13:10:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:10:23+00:00</t>
+    <t>2026-06-18T14:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$88</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3266" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:01:22+00:00</t>
+    <t>2026-06-22T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}fr-invariant-intent:L'intention doit être order, plan ou proposal. {intent = 'order' or intent = 'plan' or intent = 'proposal'}</t>
   </si>
   <si>
     <t>Request</t>
@@ -725,9 +725,7 @@
     <t>ServiceRequest.intent</t>
   </si>
   <si>
-    <t>Si la demande fait partie d'un plan de soins : 'INT = order'
-Si la demande est une proposition : 'PRP = proposal'
-Si la demande est un objectif à atteindre : 'GOL = plan'</t>
+    <t>Intention de la demande : order, plan ou proposal</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
@@ -850,7 +848,7 @@
 </t>
   </si>
   <si>
-    <t>Type de la demande</t>
+    <t>Type de la demande : Si aucun code n'est trouvé dans des terminologies existantes, utiliser le code : GEN-092.04.20 'Autre demande d’examen ou de suivi'</t>
   </si>
   <si>
     <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
@@ -880,7 +878,36 @@
     <t>Procedure.procedureCode</t>
   </si>
   <si>
-    <t>ServiceRequest.code.id</t>
+    <t>ServiceRequest.orderDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">detailed instructions
+</t>
+  </si>
+  <si>
+    <t>Additional order information</t>
+  </si>
+  <si>
+    <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
+  </si>
+  <si>
+    <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
+  </si>
+  <si>
+    <t>Codified order entry details which are based on order context.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prr-1
+</t>
+  </si>
+  <si>
+    <t>NTE</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -899,7 +926,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>ServiceRequest.code.extension</t>
+    <t>ServiceRequest.orderDetail.extension</t>
   </si>
   <si>
     <t>Additional content defined by implementations</t>
@@ -914,14 +941,14 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ServiceRequest.code.coding</t>
+    <t>ServiceRequest.orderDetail.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Type de la demande : Si aucun code n'est trouvé dans des terminologies existantes, utiliser le code : GEN-092.04.20 'Autre demande d’examen ou de suivi'</t>
+    <t>Résultat de la demande</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -942,7 +969,7 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>ServiceRequest.code.text</t>
+    <t>ServiceRequest.orderDetail.text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -964,50 +991,6 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">detailed instructions
-</t>
-  </si>
-  <si>
-    <t>Additional order information</t>
-  </si>
-  <si>
-    <t>Additional details and instructions about the how the services are to be delivered.   For example, and order for a urinary catheter may have an order detail for an external or indwelling catheter, or an order for a bandage may require additional instructions specifying how the bandage should be applied.</t>
-  </si>
-  <si>
-    <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
-  </si>
-  <si>
-    <t>Codified order entry details which are based on order context.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prr-1
-</t>
-  </si>
-  <si>
-    <t>NTE</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.coding</t>
-  </si>
-  <si>
-    <t>Résultat de la demande</t>
-  </si>
-  <si>
-    <t>ServiceRequest.orderDetail.text</t>
   </si>
   <si>
     <t>ServiceRequest.quantity[x]</t>
@@ -2188,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO92"/>
+  <dimension ref="A1:AO88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.625" customWidth="true" bestFit="true"/>
@@ -5164,7 +5147,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>276</v>
       </c>
@@ -5173,7 +5156,7 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5183,16 +5166,16 @@
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>278</v>
@@ -5200,7 +5183,9 @@
       <c r="M26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="N26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5225,13 +5210,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>81</v>
+        <v>281</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>81</v>
+        <v>282</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5249,53 +5234,53 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5307,17 +5292,15 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5354,31 +5337,31 @@
         <v>81</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5387,7 +5370,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -5398,14 +5381,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5421,23 +5404,21 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5473,19 +5454,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5497,16 +5478,16 @@
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5531,7 +5512,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5543,19 +5524,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5604,13 +5585,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5622,10 +5603,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5634,16 +5615,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5653,7 +5634,7 @@
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
@@ -5662,7 +5643,7 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>306</v>
@@ -5673,7 +5654,9 @@
       <c r="N30" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5697,40 +5680,40 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="Z30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5739,16 +5722,16 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5776,19 +5759,21 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5836,7 +5821,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5848,16 +5833,16 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>281</v>
+        <v>318</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5868,21 +5853,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5891,20 +5876,18 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5941,65 +5924,65 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -6011,20 +5994,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -6072,13 +6051,13 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>81</v>
@@ -6087,41 +6066,41 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>334</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
@@ -6130,20 +6109,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6191,7 +6166,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6206,27 +6181,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6249,18 +6224,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6284,13 +6257,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>81</v>
+        <v>352</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6308,7 +6281,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6326,32 +6299,32 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6366,13 +6339,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>360</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6423,10 +6396,10 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>90</v>
@@ -6438,31 +6411,31 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>332</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6472,7 +6445,7 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>81</v>
@@ -6481,15 +6454,17 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6538,7 +6513,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6553,56 +6528,56 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>342</v>
+        <v>376</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6653,7 +6628,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6665,41 +6640,41 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6708,18 +6683,20 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>292</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6744,43 +6721,43 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>358</v>
+        <v>81</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6789,25 +6766,27 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>290</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>360</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6823,16 +6802,16 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6883,46 +6862,46 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>295</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6932,26 +6911,24 @@
         <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>373</v>
+        <v>286</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -7000,7 +6977,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>289</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7012,30 +6989,30 @@
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>290</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7043,10 +7020,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7058,13 +7035,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7103,31 +7080,31 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -7136,7 +7113,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7147,21 +7124,23 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="D43" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7176,14 +7155,12 @@
         <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>283</v>
+        <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7220,19 +7197,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7253,7 +7230,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7264,14 +7241,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7292,13 +7267,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>286</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
+        <v>287</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>288</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7349,19 +7324,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7370,7 +7345,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7381,10 +7356,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7395,7 +7370,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7407,13 +7382,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7452,31 +7427,31 @@
         <v>81</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7485,7 +7460,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7496,10 +7471,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7507,10 +7482,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>393</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7522,22 +7497,24 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>136</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>81</v>
@@ -7567,31 +7544,31 @@
         <v>81</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7600,7 +7577,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7611,20 +7588,18 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7639,13 +7614,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>136</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7657,7 +7632,7 @@
         <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>81</v>
@@ -7672,13 +7647,11 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7696,19 +7669,19 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>286</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7717,7 +7690,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7728,12 +7701,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7754,13 +7729,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>278</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7811,19 +7786,19 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7832,7 +7807,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7843,10 +7818,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7857,7 +7832,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7869,13 +7844,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>137</v>
+        <v>288</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7914,31 +7889,31 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7947,7 +7922,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7958,10 +7933,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7969,10 +7944,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7984,24 +7959,22 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>136</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>81</v>
@@ -8031,31 +8004,31 @@
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -8064,7 +8037,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -8075,10 +8048,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8086,7 +8059,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>
@@ -8101,25 +8074,27 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8134,11 +8109,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8156,10 +8133,10 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>90</v>
@@ -8168,7 +8145,7 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>81</v>
@@ -8188,14 +8165,12 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8216,13 +8191,13 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8273,19 +8248,19 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>286</v>
+        <v>407</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
@@ -8294,7 +8269,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8305,18 +8280,20 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>90</v>
@@ -8331,13 +8308,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8388,19 +8365,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8409,7 +8386,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>281</v>
+        <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8420,10 +8397,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8434,7 +8411,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8446,13 +8423,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>137</v>
+        <v>288</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8491,31 +8468,31 @@
         <v>81</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -8524,7 +8501,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8535,10 +8512,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8546,10 +8523,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8561,24 +8538,22 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>81</v>
@@ -8608,31 +8583,31 @@
         <v>81</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>81</v>
@@ -8641,7 +8616,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8652,10 +8627,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8663,7 +8638,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>90</v>
@@ -8678,22 +8653,24 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>81</v>
+        <v>416</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>81</v>
@@ -8735,10 +8712,10 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>90</v>
@@ -8747,7 +8724,7 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
@@ -8767,20 +8744,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>90</v>
@@ -8795,13 +8770,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>422</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8852,19 +8827,19 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>286</v>
+        <v>407</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8873,7 +8848,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8887,7 +8862,7 @@
         <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8895,7 +8870,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>90</v>
@@ -8910,22 +8885,24 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>278</v>
+        <v>397</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>81</v>
@@ -8967,10 +8944,10 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>90</v>
@@ -8988,7 +8965,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8999,10 +8976,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9025,13 +9002,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>136</v>
+        <v>403</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9070,31 +9047,31 @@
         <v>81</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>286</v>
+        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9103,7 +9080,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -9114,10 +9091,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9125,7 +9102,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -9137,19 +9114,19 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>286</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9157,7 +9134,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>81</v>
@@ -9199,19 +9176,19 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
@@ -9231,10 +9208,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9254,18 +9231,20 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>427</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9290,13 +9269,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9314,7 +9293,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9346,10 +9325,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9357,7 +9336,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>90</v>
@@ -9369,19 +9348,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9389,7 +9368,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>81</v>
@@ -9431,10 +9410,10 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>90</v>
@@ -9443,7 +9422,7 @@
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9452,7 +9431,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9463,10 +9442,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9477,7 +9456,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9486,18 +9465,20 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>433</v>
+        <v>286</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9546,7 +9527,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9578,14 +9559,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9604,16 +9585,16 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9639,13 +9620,13 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>81</v>
+        <v>458</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9644,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9672,22 +9653,22 @@
         <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>81</v>
+        <v>460</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>133</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9695,21 +9676,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>81</v>
+        <v>465</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9721,16 +9702,16 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>104</v>
+        <v>466</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9756,13 +9737,13 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9780,13 +9761,13 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
@@ -9795,16 +9776,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>472</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9812,10 +9793,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9826,7 +9807,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9838,17 +9819,15 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9873,13 +9852,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -9897,13 +9876,13 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
@@ -9918,10 +9897,10 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>168</v>
+        <v>478</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -9929,10 +9908,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9943,7 +9922,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -9955,17 +9934,15 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>277</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10014,13 +9991,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -10035,10 +10012,10 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>133</v>
+        <v>482</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10046,21 +10023,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10075,13 +10052,13 @@
         <v>235</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10110,10 +10087,10 @@
         <v>240</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10131,13 +10108,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -10146,16 +10123,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10163,14 +10140,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10189,16 +10166,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10248,7 +10225,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10263,16 +10240,16 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
@@ -10280,10 +10257,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10303,16 +10280,16 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>235</v>
+        <v>502</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10339,13 +10316,13 @@
         <v>81</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -10363,7 +10340,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>478</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10378,16 +10355,16 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
@@ -10395,14 +10372,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10418,18 +10395,20 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10478,7 +10457,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10493,16 +10472,16 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10510,10 +10489,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10536,16 +10515,16 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>235</v>
+        <v>518</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10571,13 +10550,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -10595,7 +10574,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10610,31 +10589,31 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10644,7 +10623,7 @@
         <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>81</v>
@@ -10653,18 +10632,20 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>499</v>
+        <v>235</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10688,13 +10669,11 @@
         <v>81</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>81</v>
@@ -10712,7 +10691,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10727,27 +10706,27 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10755,7 +10734,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>80</v>
@@ -10770,13 +10749,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10815,19 +10794,17 @@
         <v>81</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10842,41 +10819,43 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>511</v>
+        <v>284</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="D75" t="s" s="2">
-        <v>514</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>81</v>
@@ -10885,17 +10864,15 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10944,7 +10921,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10959,27 +10936,27 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>520</v>
+        <v>284</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10990,7 +10967,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -10999,20 +10976,18 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>523</v>
+        <v>286</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>524</v>
+        <v>287</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11061,28 +11036,28 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>522</v>
+        <v>289</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>528</v>
+        <v>290</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11091,16 +11066,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>530</v>
+        <v>154</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11110,29 +11085,27 @@
         <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>531</v>
+        <v>292</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>532</v>
+        <v>293</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11156,29 +11129,31 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>535</v>
+        <v>81</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>529</v>
+        <v>295</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11190,30 +11165,30 @@
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>536</v>
+        <v>290</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>537</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11221,10 +11196,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11233,18 +11208,20 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11281,23 +11258,25 @@
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AC78" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11306,58 +11285,56 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>543</v>
+        <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>545</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K79" t="s" s="2">
-        <v>539</v>
+        <v>358</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11408,13 +11385,13 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
@@ -11423,27 +11400,27 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>543</v>
+        <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>545</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11451,7 +11428,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>90</v>
@@ -11463,16 +11440,16 @@
         <v>81</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>277</v>
+        <v>564</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>278</v>
+        <v>565</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>279</v>
+        <v>566</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11523,10 +11500,10 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>280</v>
+        <v>567</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>90</v>
@@ -11535,16 +11512,16 @@
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>281</v>
+        <v>568</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11553,26 +11530,28 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="D81" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>81</v>
@@ -11581,17 +11560,15 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>135</v>
+        <v>534</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>283</v>
+        <v>571</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11628,19 +11605,19 @@
         <v>81</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>286</v>
+        <v>533</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11652,30 +11629,30 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>81</v>
+        <v>538</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>281</v>
+        <v>539</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11695,20 +11672,18 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>555</v>
+        <v>286</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>556</v>
+        <v>287</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11757,7 +11732,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>559</v>
+        <v>289</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11769,16 +11744,16 @@
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>560</v>
+        <v>290</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -11789,21 +11764,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -11812,18 +11787,20 @@
         <v>81</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>363</v>
+        <v>135</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>563</v>
+        <v>292</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11860,40 +11837,40 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>565</v>
+        <v>295</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>566</v>
+        <v>290</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -11904,10 +11881,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11915,7 +11892,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>90</v>
@@ -11930,15 +11907,17 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11987,10 +11966,10 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>90</v>
@@ -12008,7 +11987,7 @@
         <v>133</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
@@ -12017,43 +11996,41 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J85" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K85" t="s" s="2">
-        <v>539</v>
+        <v>358</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12104,13 +12081,13 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>81</v>
@@ -12119,27 +12096,27 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>543</v>
+        <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>312</v>
+        <v>133</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>545</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12147,7 +12124,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>90</v>
@@ -12159,16 +12136,16 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>277</v>
+        <v>564</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>278</v>
+        <v>577</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>279</v>
+        <v>566</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12219,10 +12196,10 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>280</v>
+        <v>567</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>90</v>
@@ -12231,16 +12208,16 @@
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>281</v>
+        <v>568</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
@@ -12254,18 +12231,18 @@
         <v>578</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12274,20 +12251,18 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>283</v>
+        <v>579</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12324,40 +12299,40 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>286</v>
+        <v>578</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>281</v>
+        <v>581</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
@@ -12368,10 +12343,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12382,7 +12357,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
@@ -12391,19 +12366,19 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12453,13 +12428,13 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
@@ -12468,485 +12443,23 @@
         <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>81</v>
+        <v>587</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO92">
+  <autoFilter ref="A1:AO88">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12956,7 +12469,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI91">
+  <conditionalFormatting sqref="A2:AI87">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:03:44+00:00</t>
+    <t>2026-06-22T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:16:05+00:00</t>
+    <t>2026-06-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:23:37+00:00</t>
+    <t>2026-06-22T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
